--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_212_R22.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_212_R22.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.7536</v>
+        <v>6.0067</v>
       </c>
       <c r="E2" t="n">
-        <v>5.7105</v>
+        <v>6.0644</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0431</v>
+        <v>-0.0577</v>
       </c>
       <c r="G2" t="n">
         <v>5.8421</v>
@@ -610,13 +610,13 @@
         <v>0.9278</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.4802</v>
+        <v>-0.2271</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.6642</v>
+        <v>-0.3104</v>
       </c>
       <c r="U2" t="n">
-        <v>0.1841</v>
+        <v>0.0833</v>
       </c>
       <c r="V2" t="n">
         <v>-0.5361</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>W. GABRIEL</t>
+          <t>A. OBST</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.9898</v>
+        <v>2.2306</v>
       </c>
       <c r="E3" t="n">
-        <v>3.9694</v>
+        <v>1.8032</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.9795</v>
+        <v>0.4274</v>
       </c>
       <c r="G3" t="n">
-        <v>4.301</v>
+        <v>3.7235</v>
       </c>
       <c r="H3" t="n">
-        <v>2.8822</v>
+        <v>0.3542</v>
       </c>
       <c r="I3" t="n">
-        <v>1.4188</v>
+        <v>3.3694</v>
       </c>
       <c r="J3" t="n">
-        <v>4.3083</v>
+        <v>5.3255</v>
       </c>
       <c r="K3" t="n">
-        <v>3.4618</v>
+        <v>1.9529</v>
       </c>
       <c r="L3" t="n">
-        <v>0.8465</v>
+        <v>3.3726</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.0073</v>
+        <v>-1.602</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.5796</v>
+        <v>-1.5987</v>
       </c>
       <c r="O3" t="n">
-        <v>0.5723</v>
+        <v>-0.0033</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>-2.0876</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.1598</v>
+        <v>-3.4793</v>
       </c>
       <c r="R3" t="n">
-        <v>1.1598</v>
+        <v>1.3917</v>
       </c>
       <c r="S3" t="n">
-        <v>1.3693</v>
+        <v>0.5946</v>
       </c>
       <c r="T3" t="n">
-        <v>1.2151</v>
+        <v>-0.0431</v>
       </c>
       <c r="U3" t="n">
-        <v>0.1542</v>
+        <v>0.6375999999999999</v>
       </c>
       <c r="V3" t="n">
-        <v>-2.6805</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>-0.3943</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>-2.2862</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A. OBST</t>
+          <t>W. GABRIEL</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.7251</v>
+        <v>2.0126</v>
       </c>
       <c r="E4" t="n">
-        <v>1.3314</v>
+        <v>3.0258</v>
       </c>
       <c r="F4" t="n">
-        <v>0.3938</v>
+        <v>-1.0131</v>
       </c>
       <c r="G4" t="n">
-        <v>3.7235</v>
+        <v>4.301</v>
       </c>
       <c r="H4" t="n">
-        <v>0.3542</v>
+        <v>2.8822</v>
       </c>
       <c r="I4" t="n">
-        <v>3.3694</v>
+        <v>1.4188</v>
       </c>
       <c r="J4" t="n">
-        <v>5.3255</v>
+        <v>4.3083</v>
       </c>
       <c r="K4" t="n">
-        <v>1.9529</v>
+        <v>3.4618</v>
       </c>
       <c r="L4" t="n">
-        <v>3.3726</v>
+        <v>0.8465</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.602</v>
+        <v>-0.0073</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.5987</v>
+        <v>-0.5796</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.0033</v>
+        <v>0.5723</v>
       </c>
       <c r="P4" t="n">
-        <v>-2.0876</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>-3.4793</v>
+        <v>-1.1598</v>
       </c>
       <c r="R4" t="n">
-        <v>1.3917</v>
+        <v>1.1598</v>
       </c>
       <c r="S4" t="n">
-        <v>0.0892</v>
+        <v>0.3921</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.5149</v>
+        <v>0.2715</v>
       </c>
       <c r="U4" t="n">
-        <v>0.604</v>
+        <v>0.1206</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>-2.6805</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>-0.3943</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-2.2862</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>N. GIFFEY</t>
+          <t>O. DA SILVA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,64 +799,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.0837</v>
+        <v>1.3251</v>
       </c>
       <c r="E5" t="n">
-        <v>0.6808</v>
+        <v>0.4379</v>
       </c>
       <c r="F5" t="n">
-        <v>0.4029</v>
+        <v>0.8871</v>
       </c>
       <c r="G5" t="n">
-        <v>0.9339</v>
+        <v>-0.06850000000000001</v>
       </c>
       <c r="H5" t="n">
-        <v>0.2413</v>
+        <v>-0.3697</v>
       </c>
       <c r="I5" t="n">
-        <v>0.6926</v>
+        <v>0.3012</v>
       </c>
       <c r="J5" t="n">
-        <v>0.6729000000000001</v>
+        <v>-0.5047</v>
       </c>
       <c r="K5" t="n">
-        <v>0.08400000000000001</v>
+        <v>-0.6519</v>
       </c>
       <c r="L5" t="n">
-        <v>0.5889</v>
+        <v>0.1472</v>
       </c>
       <c r="M5" t="n">
-        <v>0.261</v>
+        <v>0.4362</v>
       </c>
       <c r="N5" t="n">
-        <v>0.1573</v>
+        <v>0.2822</v>
       </c>
       <c r="O5" t="n">
-        <v>0.1038</v>
+        <v>0.154</v>
       </c>
       <c r="P5" t="n">
-        <v>0.232</v>
+        <v>0.6959</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0.232</v>
+        <v>0.6959</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.08210000000000001</v>
+        <v>-0.3745</v>
       </c>
       <c r="T5" t="n">
-        <v>0.007900000000000001</v>
+        <v>-0.1296</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.0901</v>
+        <v>-0.2449</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.0722</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.0722</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>O. DA SILVA</t>
+          <t>N. DIMITRIJEVIC</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,40 +877,40 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9883</v>
+        <v>1.3073</v>
       </c>
       <c r="E6" t="n">
-        <v>0.202</v>
+        <v>0.7915</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7863</v>
+        <v>0.5158</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.06850000000000001</v>
+        <v>-0.1029</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.3697</v>
+        <v>-0.9293</v>
       </c>
       <c r="I6" t="n">
-        <v>0.3012</v>
+        <v>0.8264</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.5047</v>
+        <v>-0.0529</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.6519</v>
+        <v>-0.6751</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1472</v>
+        <v>0.6222</v>
       </c>
       <c r="M6" t="n">
-        <v>0.4362</v>
+        <v>-0.05</v>
       </c>
       <c r="N6" t="n">
-        <v>0.2822</v>
+        <v>-0.2543</v>
       </c>
       <c r="O6" t="n">
-        <v>0.154</v>
+        <v>0.2042</v>
       </c>
       <c r="P6" t="n">
         <v>0.6959</v>
@@ -922,13 +922,13 @@
         <v>0.6959</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.7112000000000001</v>
+        <v>-0.3578</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.3655</v>
+        <v>-0.2278</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.3457</v>
+        <v>-0.13</v>
       </c>
       <c r="V6" t="n">
         <v>1.0722</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>N. DIMITRIJEVIC</t>
+          <t>N. GIFFEY</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,64 +955,64 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.819</v>
+        <v>1.3025</v>
       </c>
       <c r="E7" t="n">
-        <v>0.4377</v>
+        <v>0.7988</v>
       </c>
       <c r="F7" t="n">
-        <v>0.3814</v>
+        <v>0.5037</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.1029</v>
+        <v>0.9339</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.9293</v>
+        <v>0.2413</v>
       </c>
       <c r="I7" t="n">
-        <v>0.8264</v>
+        <v>0.6926</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.0529</v>
+        <v>0.6729000000000001</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.6751</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="L7" t="n">
-        <v>0.6222</v>
+        <v>0.5889</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.05</v>
+        <v>0.261</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.2543</v>
+        <v>0.1573</v>
       </c>
       <c r="O7" t="n">
-        <v>0.2042</v>
+        <v>0.1038</v>
       </c>
       <c r="P7" t="n">
-        <v>0.6959</v>
+        <v>0.232</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0.6959</v>
+        <v>0.232</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.8461</v>
+        <v>0.1366</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.5816</v>
+        <v>0.1259</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.2645</v>
+        <v>0.0108</v>
       </c>
       <c r="V7" t="n">
-        <v>1.0722</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.0722</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.7598</v>
+        <v>0.659</v>
       </c>
       <c r="E8" t="n">
         <v>1.339</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.5790999999999999</v>
+        <v>-0.68</v>
       </c>
       <c r="G8" t="n">
         <v>-0.3403</v>
@@ -1078,13 +1078,13 @@
         <v>1.3917</v>
       </c>
       <c r="S8" t="n">
-        <v>1.01</v>
+        <v>0.9091</v>
       </c>
       <c r="T8" t="n">
         <v>0.2794</v>
       </c>
       <c r="U8" t="n">
-        <v>0.7306</v>
+        <v>0.6297</v>
       </c>
       <c r="V8" t="n">
         <v>-0.1418</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.7782</v>
+        <v>-0.9805</v>
       </c>
       <c r="E9" t="n">
-        <v>0.8516</v>
+        <v>0.6157</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.6299</v>
+        <v>-1.5963</v>
       </c>
       <c r="G9" t="n">
         <v>-0.5019</v>
@@ -1156,13 +1156,13 @@
         <v>1.1598</v>
       </c>
       <c r="S9" t="n">
-        <v>0.8834</v>
+        <v>0.6811</v>
       </c>
       <c r="T9" t="n">
-        <v>0.5702</v>
+        <v>0.3343</v>
       </c>
       <c r="U9" t="n">
-        <v>0.3132</v>
+        <v>0.3468</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.66</v>
+        <v>-1.3563</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.3841</v>
+        <v>-0.9123</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.276</v>
+        <v>-0.444</v>
       </c>
       <c r="G10" t="n">
         <v>-1.9961</v>
@@ -1234,13 +1234,13 @@
         <v>1.1598</v>
       </c>
       <c r="S10" t="n">
-        <v>0.3361</v>
+        <v>0.6398</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.2908</v>
+        <v>0.181</v>
       </c>
       <c r="U10" t="n">
-        <v>0.6269</v>
+        <v>0.4589</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.9768</v>
+        <v>-2.9547</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.7578</v>
+        <v>-1.9373</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.2191</v>
+        <v>-1.0174</v>
       </c>
       <c r="G11" t="n">
         <v>-2.3985</v>
@@ -1312,13 +1312,13 @@
         <v>0.9278</v>
       </c>
       <c r="S11" t="n">
-        <v>1.8134</v>
+        <v>0.8355</v>
       </c>
       <c r="T11" t="n">
-        <v>1.8442</v>
+        <v>0.6647</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.0307</v>
+        <v>0.1709</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.2379</v>
+        <v>-3.0857</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.6226</v>
+        <v>-3.2687</v>
       </c>
       <c r="F12" t="n">
-        <v>0.3846</v>
+        <v>0.183</v>
       </c>
       <c r="G12" t="n">
         <v>-2.4586</v>
@@ -1390,13 +1390,13 @@
         <v>0.6959</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.3154</v>
+        <v>-0.1632</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.3576</v>
+        <v>-0.0037</v>
       </c>
       <c r="U12" t="n">
-        <v>0.0422</v>
+        <v>-0.1595</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1423,10 +1423,10 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>6.4664</v>
+        <v>6.466600000000002</v>
       </c>
       <c r="E13" t="n">
-        <v>8.757899999999999</v>
+        <v>8.757999999999999</v>
       </c>
       <c r="F13" t="n">
         <v>-2.2915</v>
@@ -1435,7 +1435,7 @@
         <v>6.933699999999998</v>
       </c>
       <c r="H13" t="n">
-        <v>0.8943000000000004</v>
+        <v>0.8943</v>
       </c>
       <c r="I13" t="n">
         <v>6.039500000000001</v>
@@ -1453,7 +1453,7 @@
         <v>-10.617</v>
       </c>
       <c r="N13" t="n">
-        <v>-6.636400000000001</v>
+        <v>-6.636399999999999</v>
       </c>
       <c r="O13" t="n">
         <v>-3.9808</v>
@@ -1468,7 +1468,7 @@
         <v>10.4381</v>
       </c>
       <c r="S13" t="n">
-        <v>3.0664</v>
+        <v>3.0662</v>
       </c>
       <c r="T13" t="n">
         <v>1.1422</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.7022</v>
+        <v>2.8538</v>
       </c>
       <c r="E14" t="n">
-        <v>2.1072</v>
+        <v>2.2252</v>
       </c>
       <c r="F14" t="n">
-        <v>0.595</v>
+        <v>0.6286</v>
       </c>
       <c r="G14" t="n">
         <v>2.2985</v>
@@ -1546,13 +1546,13 @@
         <v>0.4639</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.0602</v>
+        <v>0.0914</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.2987</v>
+        <v>-0.1808</v>
       </c>
       <c r="U14" t="n">
-        <v>0.2385</v>
+        <v>0.2721</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.6516</v>
+        <v>2.5724</v>
       </c>
       <c r="E15" t="n">
-        <v>2.773</v>
+        <v>3.2448</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.1214</v>
+        <v>-0.6725</v>
       </c>
       <c r="G15" t="n">
         <v>1.7062</v>
@@ -1624,13 +1624,13 @@
         <v>2.3195</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.6087</v>
+        <v>-0.6879</v>
       </c>
       <c r="T15" t="n">
-        <v>-1.187</v>
+        <v>-0.7151999999999999</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.4217</v>
+        <v>0.0272</v>
       </c>
       <c r="V15" t="n">
         <v>0.3943</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.0195</v>
+        <v>-0.1999</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.0589</v>
+        <v>-0.4128</v>
       </c>
       <c r="F16" t="n">
-        <v>0.0784</v>
+        <v>0.2129</v>
       </c>
       <c r="G16" t="n">
         <v>-0.7818000000000001</v>
@@ -1702,13 +1702,13 @@
         <v>0.232</v>
       </c>
       <c r="S16" t="n">
-        <v>0.5693</v>
+        <v>0.3499</v>
       </c>
       <c r="T16" t="n">
-        <v>0.637</v>
+        <v>0.2831</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.0677</v>
+        <v>0.0668</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>P. KALAITZAKIS</t>
+          <t>J. HERNANGOMEZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.3284</v>
+        <v>-0.5875</v>
       </c>
       <c r="E17" t="n">
-        <v>1.5841</v>
+        <v>0.7192</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.9124</v>
+        <v>-1.3066</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.1251</v>
+        <v>-2.5149</v>
       </c>
       <c r="H17" t="n">
-        <v>0.4537</v>
+        <v>-1.1497</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.5788</v>
+        <v>-1.3652</v>
       </c>
       <c r="J17" t="n">
-        <v>0.7897999999999999</v>
+        <v>0.8879</v>
       </c>
       <c r="K17" t="n">
-        <v>0.7897999999999999</v>
+        <v>0.3025</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>0.5854</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.9149</v>
+        <v>-3.4027</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.3361</v>
+        <v>-1.4522</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.5788</v>
+        <v>-1.9505</v>
       </c>
       <c r="P17" t="n">
-        <v>0.232</v>
+        <v>2.0876</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>0.232</v>
+        <v>2.0876</v>
       </c>
       <c r="S17" t="n">
-        <v>0.637</v>
+        <v>-0.1601</v>
       </c>
       <c r="T17" t="n">
-        <v>0.7943</v>
+        <v>-0.1687</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.1573</v>
+        <v>0.0086</v>
       </c>
       <c r="V17" t="n">
-        <v>-1.0722</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.0722</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>R. HOLMES</t>
+          <t>P. KALAITZAKIS</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,64 +1813,64 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.4399</v>
+        <v>-0.6429</v>
       </c>
       <c r="E18" t="n">
-        <v>1.7169</v>
+        <v>1.1123</v>
       </c>
       <c r="F18" t="n">
-        <v>-2.1568</v>
+        <v>-1.7552</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.2104</v>
+        <v>-0.1251</v>
       </c>
       <c r="H18" t="n">
-        <v>0.1512</v>
+        <v>0.4537</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.3617</v>
+        <v>-0.5788</v>
       </c>
       <c r="J18" t="n">
-        <v>1.4882</v>
+        <v>0.7897999999999999</v>
       </c>
       <c r="K18" t="n">
-        <v>1.2673</v>
+        <v>0.7897999999999999</v>
       </c>
       <c r="L18" t="n">
-        <v>0.2208</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>-2.6986</v>
+        <v>-0.9149</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.1161</v>
+        <v>-0.3361</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.5825</v>
+        <v>-0.5788</v>
       </c>
       <c r="P18" t="n">
-        <v>1.1598</v>
+        <v>0.232</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>2.3195</v>
+        <v>0.232</v>
       </c>
       <c r="S18" t="n">
-        <v>0.5412</v>
+        <v>0.3224</v>
       </c>
       <c r="T18" t="n">
-        <v>1.2467</v>
+        <v>0.3224</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.7055</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.9304</v>
+        <v>-1.0722</v>
       </c>
       <c r="W18" t="n">
-        <v>0.1418</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
         <v>-1.0722</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>J. HERNANGOMEZ</t>
+          <t>R. HOLMES</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.9585</v>
+        <v>-1.1539</v>
       </c>
       <c r="E20" t="n">
-        <v>0.7192</v>
+        <v>0.4195</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.6776</v>
+        <v>-1.5734</v>
       </c>
       <c r="G20" t="n">
-        <v>-2.5149</v>
+        <v>-1.2104</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.1497</v>
+        <v>0.1512</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.3652</v>
+        <v>-1.3617</v>
       </c>
       <c r="J20" t="n">
-        <v>0.8879</v>
+        <v>1.4882</v>
       </c>
       <c r="K20" t="n">
-        <v>0.3025</v>
+        <v>1.2673</v>
       </c>
       <c r="L20" t="n">
-        <v>0.5854</v>
+        <v>0.2208</v>
       </c>
       <c r="M20" t="n">
-        <v>-3.4027</v>
+        <v>-2.6986</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.4522</v>
+        <v>-1.1161</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.9505</v>
+        <v>-1.5825</v>
       </c>
       <c r="P20" t="n">
-        <v>2.0876</v>
+        <v>1.1598</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R20" t="n">
-        <v>2.0876</v>
+        <v>2.3195</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.5311</v>
+        <v>-0.1729</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.1687</v>
+        <v>-0.0507</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.3624</v>
+        <v>-0.1221</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>-0.9304</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>0.1418</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.4118</v>
+        <v>-1.1866</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.2566</v>
+        <v>-1.0207</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.1552</v>
+        <v>-0.166</v>
       </c>
       <c r="G21" t="n">
         <v>-0.3482</v>
@@ -2092,13 +2092,13 @@
         <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>0.09619999999999999</v>
+        <v>0.3213</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.224</v>
+        <v>0.0119</v>
       </c>
       <c r="U21" t="n">
-        <v>0.3203</v>
+        <v>0.3095</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>K. SLOUKAS</t>
+          <t>T. SHORTS</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.9924</v>
+        <v>-1.5392</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.9953</v>
+        <v>-1.7081</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.9971</v>
+        <v>0.1689</v>
       </c>
       <c r="G22" t="n">
-        <v>1.1885</v>
+        <v>-1.9363</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.1234</v>
+        <v>0.4896</v>
       </c>
       <c r="I22" t="n">
-        <v>2.3119</v>
+        <v>-2.4259</v>
       </c>
       <c r="J22" t="n">
-        <v>2.1506</v>
+        <v>-0.2065</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.1646</v>
+        <v>0.9011</v>
       </c>
       <c r="L22" t="n">
-        <v>2.3152</v>
+        <v>-1.1077</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.9621</v>
+        <v>-1.7298</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.9588</v>
+        <v>-0.4116</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.0033</v>
+        <v>-1.3182</v>
       </c>
       <c r="P22" t="n">
-        <v>-2.5515</v>
+        <v>0.4639</v>
       </c>
       <c r="Q22" t="n">
-        <v>-3.4793</v>
+        <v>-1.1598</v>
       </c>
       <c r="R22" t="n">
-        <v>0.9278</v>
+        <v>1.6237</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.6294999999999999</v>
+        <v>-0.0668</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.7389</v>
+        <v>-0.3418</v>
       </c>
       <c r="U22" t="n">
-        <v>0.1094</v>
+        <v>0.275</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>1.0722</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.0722</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>T. SHORTS</t>
+          <t>K. SLOUKAS</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.3255</v>
+        <v>-1.5821</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.1799</v>
+        <v>-0.6415</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.1456</v>
+        <v>-0.9407</v>
       </c>
       <c r="G23" t="n">
-        <v>-1.9363</v>
+        <v>1.1885</v>
       </c>
       <c r="H23" t="n">
-        <v>0.4896</v>
+        <v>-1.1234</v>
       </c>
       <c r="I23" t="n">
-        <v>-2.4259</v>
+        <v>2.3119</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.2065</v>
+        <v>2.1506</v>
       </c>
       <c r="K23" t="n">
-        <v>0.9011</v>
+        <v>-0.1646</v>
       </c>
       <c r="L23" t="n">
-        <v>-1.1077</v>
+        <v>2.3152</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.7298</v>
+        <v>-0.9621</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.4116</v>
+        <v>-0.9588</v>
       </c>
       <c r="O23" t="n">
-        <v>-1.3182</v>
+        <v>-0.0033</v>
       </c>
       <c r="P23" t="n">
-        <v>0.4639</v>
+        <v>-2.5515</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1.1598</v>
+        <v>-3.4793</v>
       </c>
       <c r="R23" t="n">
-        <v>1.6237</v>
+        <v>0.9278</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.8531</v>
+        <v>-0.2192</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.8136</v>
+        <v>-0.3851</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.0395</v>
+        <v>0.1658</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1.0722</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="24">
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.5176</v>
+        <v>-1.7757</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.3566</v>
+        <v>-0.8848</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.161</v>
+        <v>-0.8909</v>
       </c>
       <c r="G24" t="n">
         <v>-4.1046</v>
@@ -2326,13 +2326,13 @@
         <v>2.3195</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.2353</v>
+        <v>-0.4933</v>
       </c>
       <c r="T24" t="n">
-        <v>-1.1791</v>
+        <v>-0.7073</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.0562</v>
+        <v>0.2139</v>
       </c>
       <c r="V24" t="n">
         <v>2.8223</v>
@@ -2359,28 +2359,28 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-6.466600000000001</v>
+        <v>-4.1074</v>
       </c>
       <c r="E25" t="n">
-        <v>2.2915</v>
+        <v>2.291500000000001</v>
       </c>
       <c r="F25" t="n">
-        <v>-8.7578</v>
+        <v>-6.399</v>
       </c>
       <c r="G25" t="n">
         <v>-6.9337</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.8940999999999992</v>
+        <v>-0.8940999999999999</v>
       </c>
       <c r="I25" t="n">
-        <v>-6.039599999999999</v>
+        <v>-6.0396</v>
       </c>
       <c r="J25" t="n">
         <v>10.6172</v>
       </c>
       <c r="K25" t="n">
-        <v>6.636199999999999</v>
+        <v>6.636200000000001</v>
       </c>
       <c r="L25" t="n">
         <v>3.9807</v>
@@ -2389,7 +2389,7 @@
         <v>-17.5508</v>
       </c>
       <c r="N25" t="n">
-        <v>-7.530500000000001</v>
+        <v>-7.5305</v>
       </c>
       <c r="O25" t="n">
         <v>-10.0202</v>
@@ -2404,13 +2404,13 @@
         <v>12.7575</v>
       </c>
       <c r="S25" t="n">
-        <v>-3.0663</v>
+        <v>-0.7072999999999999</v>
       </c>
       <c r="T25" t="n">
-        <v>-1.9241</v>
+        <v>-1.9243</v>
       </c>
       <c r="U25" t="n">
-        <v>-1.1421</v>
+        <v>1.2168</v>
       </c>
       <c r="V25" t="n">
         <v>1.214</v>
